--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_38.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_38.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coffee?</t>
+          <t>IV2</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RiskTaking</t>
+          <t>Response</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.0916988085114777</v>
+        <v>-0.9818033857521345</v>
       </c>
       <c r="C2">
-        <v>1.435185798579154</v>
+        <v>1.308468374191297</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.4845699125309998</v>
+        <v>-1.898123164372561</v>
       </c>
       <c r="C3">
-        <v>-1.283485349282832</v>
+        <v>0.864097607535385</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.5470257771370903</v>
+        <v>-0.3923995546642285</v>
       </c>
       <c r="C4">
-        <v>0.3358511803025223</v>
+        <v>-0.7439912000452429</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.8734280600674038</v>
+        <v>-0.2952789941373563</v>
       </c>
       <c r="C5">
-        <v>0.4204515468092934</v>
+        <v>0.7087065019081031</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.3493869440348636</v>
+        <v>1.942965966458916</v>
       </c>
       <c r="C6">
-        <v>-1.006606514097724</v>
+        <v>-1.479579482016477</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.188054055867309</v>
+        <v>1.755073311446564</v>
       </c>
       <c r="C7">
-        <v>-0.7600717461175517</v>
+        <v>-1.494973581572816</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.128640359899206</v>
+        <v>-0.0630654690569511</v>
       </c>
       <c r="C8">
-        <v>0.7752870550821904</v>
+        <v>0.3493478590788677</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.3503690244754338</v>
+        <v>-0.3806374499469716</v>
       </c>
       <c r="C9">
-        <v>-1.391796704783912</v>
+        <v>0.7362526994575326</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-1.201958617242118</v>
+        <v>-0.7319205471711876</v>
       </c>
       <c r="C10">
-        <v>-1.276260974512281</v>
+        <v>-1.156842223896229</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.567540109019962</v>
+        <v>-0.01044843930937176</v>
       </c>
       <c r="C11">
-        <v>0.01937309423663361</v>
+        <v>-1.322490682181342</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.1925863409825297</v>
+        <v>-1.286621026757497</v>
       </c>
       <c r="C12">
-        <v>0.1593106379098445</v>
+        <v>-0.7445788644233383</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.1165472924421542</v>
+        <v>0.9760324821361452</v>
       </c>
       <c r="C13">
-        <v>0.8083857447447901</v>
+        <v>0.07793511418237653</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.9561907349947333</v>
+        <v>-0.05396812910883562</v>
       </c>
       <c r="C14">
-        <v>1.813615124274575</v>
+        <v>0.4030561036525728</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.3272028915324627</v>
+        <v>0.5430832414944399</v>
       </c>
       <c r="C15">
-        <v>-1.654454389354908</v>
+        <v>-0.3354091142198388</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.89973542652216</v>
+        <v>0.6346847014502773</v>
       </c>
       <c r="C16">
-        <v>1.553803966325392</v>
+        <v>-0.7399295220944645</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.1783450882374712</v>
+        <v>0.6507029864208231</v>
       </c>
       <c r="C17">
-        <v>-0.2895480403692433</v>
+        <v>-0.5833522369070454</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.6623981652784962</v>
+        <v>1.439908505353644</v>
       </c>
       <c r="C18">
-        <v>0.3750287178965441</v>
+        <v>-1.207989605032494</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.700880122730974</v>
+        <v>1.690095858435458</v>
       </c>
       <c r="C19">
-        <v>0.3201195408735474</v>
+        <v>-2.105930160452596</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.051426034426379</v>
+        <v>1.158965077095062</v>
       </c>
       <c r="C20">
-        <v>0.7616165952696698</v>
+        <v>-0.5687836324107619</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.517819254242148</v>
+        <v>1.257261317893301</v>
       </c>
       <c r="C21">
-        <v>1.006808618753924</v>
+        <v>-0.27004899706158</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.100242813736056</v>
+        <v>0.3854340634903916</v>
       </c>
       <c r="C22">
-        <v>0.3721016630509943</v>
+        <v>-0.8504420313529129</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.0491089208486903</v>
+        <v>1.781273676338269</v>
       </c>
       <c r="C23">
-        <v>-0.01875734055026681</v>
+        <v>-0.5711899088426311</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.797718528117971</v>
+        <v>-1.835077166923297</v>
       </c>
       <c r="C24">
-        <v>-0.3092517848340104</v>
+        <v>1.840717862652365</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.793786095385761</v>
+        <v>1.896789031036026</v>
       </c>
       <c r="C25">
-        <v>-0.4671205748118241</v>
+        <v>-1.616709873834729</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4059663375981529</v>
+        <v>0.1911403727798315</v>
       </c>
       <c r="C26">
-        <v>-1.450327672325808</v>
+        <v>0.7077199009514895</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.087606289646053</v>
+        <v>0.6604124355521639</v>
       </c>
       <c r="C27">
-        <v>-0.6249940901513888</v>
+        <v>0.923132233149573</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.149681163801948</v>
+        <v>0.2383266187037994</v>
       </c>
       <c r="C28">
-        <v>-0.1556924092358339</v>
+        <v>0.1356184125840566</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.8604944389578327</v>
+        <v>1.004026943785553</v>
       </c>
       <c r="C29">
-        <v>0.5436026560805005</v>
+        <v>-1.32128655946735</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.4643762547201232</v>
+        <v>0.2118411499447186</v>
       </c>
       <c r="C30">
-        <v>0.01122871134615608</v>
+        <v>-0.4165163977267972</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.06398648553469963</v>
+        <v>0.4317659264692425</v>
       </c>
       <c r="C31">
-        <v>0.1751576524201086</v>
+        <v>-0.009481063005894602</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.7133478250774388</v>
+        <v>0.4022275513491049</v>
       </c>
       <c r="C32">
-        <v>-1.024799288105374</v>
+        <v>-1.542428132596371</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-1.083064308082839</v>
+        <v>-1.427032865274345</v>
       </c>
       <c r="C33">
-        <v>-0.7790728775389926</v>
+        <v>1.315349222987079</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.6716864694324146</v>
+        <v>-0.8695477703057851</v>
       </c>
       <c r="C34">
-        <v>0.9347227688642838</v>
+        <v>0.8489860002554598</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-2.89880016944703</v>
+        <v>0.1064790672079966</v>
       </c>
       <c r="C35">
-        <v>-0.6418219319096437</v>
+        <v>-1.01752723998046</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.2079567566422569</v>
+        <v>0.359949710455263</v>
       </c>
       <c r="C36">
-        <v>-0.1635459568926966</v>
+        <v>0.310576295684679</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.5075361437076975</v>
+        <v>-1.187779634731393</v>
       </c>
       <c r="C37">
-        <v>1.198292876759487</v>
+        <v>1.379403750020494</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.5806447390234838</v>
+        <v>-0.50392113977425</v>
       </c>
       <c r="C38">
-        <v>0.1658973088240274</v>
+        <v>0.2881508618215926</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.3042009123035314</v>
+        <v>0.2885027567036813</v>
       </c>
       <c r="C39">
-        <v>-1.997258215165348</v>
+        <v>-0.7192389526747387</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.2520669792366553</v>
+        <v>1.123200019261856</v>
       </c>
       <c r="C40">
-        <v>-0.4733100487173163</v>
+        <v>-0.6073809191796622</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.146013148962066</v>
+        <v>-1.587587143638143</v>
       </c>
       <c r="C41">
-        <v>-0.01881863819421352</v>
+        <v>-0.3880362719164976</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>1.006123951195458</v>
+        <v>-0.3336818617264439</v>
       </c>
       <c r="C42">
-        <v>-1.457108135079651</v>
+        <v>0.2500305259636366</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.08636503559573591</v>
+        <v>-0.1056629104362395</v>
       </c>
       <c r="C43">
-        <v>0.9827636744442638</v>
+        <v>-0.1805055157369196</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.307464467050843</v>
+        <v>-1.260472014059221</v>
       </c>
       <c r="C44">
-        <v>-0.3088327277390421</v>
+        <v>0.4070920730227364</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.6710654129817146</v>
+        <v>0.5608883700898836</v>
       </c>
       <c r="C45">
-        <v>-0.5040463469767744</v>
+        <v>-1.849673914809735</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.366252975549455</v>
+        <v>-1.661032849758214</v>
       </c>
       <c r="C46">
-        <v>1.533242562077568</v>
+        <v>1.166582529888236</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.8900043580262638</v>
+        <v>0.9540423927884758</v>
       </c>
       <c r="C47">
-        <v>-0.004322850348068896</v>
+        <v>0.070838114039115</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.02637538559036853</v>
+        <v>-0.4865160007314741</v>
       </c>
       <c r="C48">
-        <v>0.4455717516967975</v>
+        <v>0.431806034933</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.07717005763105318</v>
+        <v>0.9458438522982375</v>
       </c>
       <c r="C49">
-        <v>0.4486970037141484</v>
+        <v>-1.747120558005122</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.5506905746464285</v>
+        <v>-0.04552997918820532</v>
       </c>
       <c r="C50">
-        <v>-1.098444962921848</v>
+        <v>-0.4732158448312541</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.8082530623479118</v>
+        <v>-0.2217548188290192</v>
       </c>
       <c r="C51">
-        <v>0.461453784015697</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-0.5680323931229474</v>
-      </c>
-      <c r="C52">
-        <v>0.44691191463131</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>0.8767080892108153</v>
-      </c>
-      <c r="C53">
-        <v>-0.2485210333972513</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>0.1296419165957078</v>
-      </c>
-      <c r="C54">
-        <v>-0.6622803726502127</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>0.05127910482679605</v>
-      </c>
-      <c r="C55">
-        <v>1.433584165370342</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>-0.3166779023007159</v>
-      </c>
-      <c r="C56">
-        <v>-1.14030568552704</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.588136532837933</v>
-      </c>
-      <c r="C57">
-        <v>0.2654015467495031</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>-0.7263848014853578</v>
-      </c>
-      <c r="C58">
-        <v>0.5208880559096825</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>0.1718242461625455</v>
-      </c>
-      <c r="C59">
-        <v>-1.382083082370313</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>0.1858798642044516</v>
-      </c>
-      <c r="C60">
-        <v>1.00574450350564</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>-0.009865633302054215</v>
-      </c>
-      <c r="C61">
-        <v>-0.9508098552173799</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>-0.4657741793111666</v>
-      </c>
-      <c r="C62">
-        <v>0.04538503069879815</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>1.265885031740202</v>
-      </c>
-      <c r="C63">
-        <v>-0.295836807113711</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>-0.8870211954933588</v>
-      </c>
-      <c r="C64">
-        <v>0.4177448664694265</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>-0.2228396270805849</v>
-      </c>
-      <c r="C65">
-        <v>-0.3153061456922046</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>1.015278468894418</v>
-      </c>
-      <c r="C66">
-        <v>0.4033484045046755</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>0.1123127735092471</v>
-      </c>
-      <c r="C67">
-        <v>1.506253493662363</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-0.9550906247571501</v>
-      </c>
-      <c r="C68">
-        <v>-0.2383280344775829</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>-1.571992325032579</v>
-      </c>
-      <c r="C69">
-        <v>0.477458497078436</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>0.7005530603365334</v>
-      </c>
-      <c r="C70">
-        <v>0.8929820044045812</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-0.0359546106622758</v>
-      </c>
-      <c r="C71">
-        <v>1.029138788052884</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>2.483715013513712</v>
-      </c>
-      <c r="C72">
-        <v>1.507441203468916</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>-1.941832727706183</v>
-      </c>
-      <c r="C73">
-        <v>0.9325600994049156</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>-0.7314206784793817</v>
-      </c>
-      <c r="C74">
-        <v>0.2227622726703902</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-0.7354854609044961</v>
-      </c>
-      <c r="C75">
-        <v>-0.3893453327922154</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>-0.3672458578256891</v>
-      </c>
-      <c r="C76">
-        <v>0.03701821572999101</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>0.1362723225809321</v>
-      </c>
-      <c r="C77">
-        <v>0.07002009820593794</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>-1.014724326718231</v>
-      </c>
-      <c r="C78">
-        <v>-1.829606490230176</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>1.008037356947342</v>
-      </c>
-      <c r="C79">
-        <v>1.699437522993425</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>2.880182699890264</v>
-      </c>
-      <c r="C80">
-        <v>1.412557502236032</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.005600687248031039</v>
-      </c>
-      <c r="C81">
-        <v>1.132182571235529</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>0.692439781509011</v>
-      </c>
-      <c r="C82">
-        <v>0.6464421743159714</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>-0.4880485116202316</v>
-      </c>
-      <c r="C83">
-        <v>-0.2802282515571279</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>-0.1285549293783237</v>
-      </c>
-      <c r="C84">
-        <v>-2.314780728786597</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-1.122286745567676</v>
-      </c>
-      <c r="C85">
-        <v>-0.02851257891566994</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-0.07562513855324132</v>
-      </c>
-      <c r="C86">
-        <v>-0.4968318407311449</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>-0.5747691849800024</v>
-      </c>
-      <c r="C87">
-        <v>0.4273286007747902</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>1.216282626205455</v>
-      </c>
-      <c r="C88">
-        <v>0.583107679341658</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>0.3544681957864638</v>
-      </c>
-      <c r="C89">
-        <v>0.7388808690085935</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>0.1414532505814589</v>
-      </c>
-      <c r="C90">
-        <v>0.1307675749123261</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-0.4513699251525609</v>
-      </c>
-      <c r="C91">
-        <v>0.3398860063294189</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>-0.214505368765679</v>
-      </c>
-      <c r="C92">
-        <v>-2.119887838347083</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>1.386690132208291</v>
-      </c>
-      <c r="C93">
-        <v>0.2276383415272502</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>0.8927385432736619</v>
-      </c>
-      <c r="C94">
-        <v>0.5378977909106337</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>0.495220042716549</v>
-      </c>
-      <c r="C95">
-        <v>1.25345038203251</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-1.010066285768711</v>
-      </c>
-      <c r="C96">
-        <v>-0.6215888509290448</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>-0.08238763916642046</v>
-      </c>
-      <c r="C97">
-        <v>0.09100378135675605</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-0.5214216177741924</v>
-      </c>
-      <c r="C98">
-        <v>0.1517876444281493</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>1.160787565416465</v>
-      </c>
-      <c r="C99">
-        <v>1.472937317802</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>-0.1209317497949277</v>
-      </c>
-      <c r="C100">
-        <v>-0.6387755533349808</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>-0.9398796302439787</v>
-      </c>
-      <c r="C101">
-        <v>0.107337504093699</v>
+        <v>-0.4191719443664627</v>
       </c>
     </row>
   </sheetData>
